--- a/consulting_forms/017_portfolio_consultation_feedback--consulting_forms.xlsx
+++ b/consulting_forms/017_portfolio_consultation_feedback--consulting_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'1_-_unsatisfied'}</t>
+          <t>1_-_unsatisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '1 - Unsatisfied'}</t>
+          <t>1 - Unsatisfied</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'2_-_neutral'}</t>
+          <t>2_-_neutral</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '2 - Neutral'}</t>
+          <t>2 - Neutral</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'3_-_satisfied'}</t>
+          <t>3_-_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': '3 - Satisfied'}</t>
+          <t>3 - Satisfied</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'4_-_very_satisfied'}</t>
+          <t>4_-_very_satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '4 - Very Satisfied'}</t>
+          <t>4 - Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'5_-_extremely_satisfied'}</t>
+          <t>5_-_extremely_satisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '5 - Extremely Satisfied'}</t>
+          <t>5 - Extremely Satisfied</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'1_-_schedule_a_follow-up_meeting'}</t>
+          <t>1_-_schedule_a_follow-up_meeting</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '1 - Schedule a follow-up meeting'}</t>
+          <t>1 - Schedule a follow-up meeting</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'2_-_continue_with_our_collaboration'}</t>
+          <t>2_-_continue_with_our_collaboration</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '2 - Continue with our collaboration'}</t>
+          <t>2 - Continue with our collaboration</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'3_-_do_not_schedule_a_follow-up_meeting'}</t>
+          <t>3_-_do_not_schedule_a_follow-up_meeting</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': '3 - Do not schedule a follow-up meeting'}</t>
+          <t>3 - Do not schedule a follow-up meeting</t>
         </is>
       </c>
     </row>
